--- a/database/seeders/data/users.xlsx
+++ b/database/seeders/data/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\general-ledger\database\seeders\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206B38B7-DB5A-44CC-A9CC-847E1A9ED657}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748B60B6-9E51-49E1-9316-C06B782DA1AD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
